--- a/Employee_Reports_wi52/Ifras Mohammed Q0598.xlsx
+++ b/Employee_Reports_wi52/Ifras Mohammed Q0598.xlsx
@@ -560,11 +560,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -609,11 +609,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -658,11 +658,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
